--- a/Plan_4semanas_20jul-16ago.xlsx
+++ b/Plan_4semanas_20jul-16ago.xlsx
@@ -968,7 +968,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Laterales</t>
+          <t>Laterales de pie</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Laterales medio posterior</t>
+          <t>Laterales banco inclinado posterior</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Laterales</t>
+          <t>Laterales sentado inclinado</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Laterales</t>
+          <t>Laterales inclinado estiramiento</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
